--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486995_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486995_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2552</v>
+        <v>4.5648</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2469</v>
+        <v>2.3787</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0082</v>
+        <v>2.1861</v>
       </c>
       <c r="G2" t="n">
         <v>3.0067</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.234</v>
+        <v>0.0756</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8486</v>
+        <v>-0.7169</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6146</v>
+        <v>0.7925</v>
       </c>
       <c r="V2" t="n">
         <v>3.5359</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2969</v>
+        <v>2.9504</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5534</v>
+        <v>-0.2325</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7435</v>
+        <v>3.1829</v>
       </c>
       <c r="G3" t="n">
-        <v>0.258</v>
+        <v>1.7668</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7367</v>
+        <v>0.3142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9947</v>
+        <v>1.4526</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0834</v>
+        <v>0.2557</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.0584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1579</v>
+        <v>0.1973</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1746</v>
+        <v>1.5111</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6623</v>
+        <v>0.2559</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8368</v>
+        <v>1.2552</v>
       </c>
       <c r="P3" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.2053</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.2321</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5379</v>
+        <v>0.0747</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1045</v>
+        <v>-0.2829</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4334</v>
+        <v>0.3576</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7063</v>
+        <v>0.6982</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1088</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2311</v>
+        <v>2.5227</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3371</v>
+        <v>1.135</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5682</v>
+        <v>1.3878</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7668</v>
+        <v>0.258</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3142</v>
+        <v>-0.7367</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4526</v>
+        <v>0.9947</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2557</v>
+        <v>0.0834</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0584</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1973</v>
+        <v>0.1579</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5111</v>
+        <v>0.1746</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2559</v>
+        <v>-0.6623</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2552</v>
+        <v>0.8368</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3555</v>
+        <v>-0.2362</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3875</v>
+        <v>-0.3139</v>
       </c>
       <c r="U4" t="n">
-        <v>0.743</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6982</v>
+        <v>2.7063</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6982</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.998</v>
+        <v>2.4188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0505</v>
+        <v>0.3527</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9475</v>
+        <v>2.066</v>
       </c>
       <c r="G5" t="n">
         <v>3.624</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01</v>
+        <v>0.4108</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6355</v>
+        <v>-0.3333</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7441</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5893</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4244</v>
+        <v>1.8496</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1151</v>
+        <v>-0.5941</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5395</v>
+        <v>2.4437</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6043</v>
+        <v>-0.3074</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3476</v>
+        <v>-0.3994</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9519</v>
+        <v>0.092</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9531</v>
+        <v>-0.7188</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2565</v>
+        <v>-0.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6967</v>
+        <v>-0.1188</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6512</v>
+        <v>0.4114</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6041</v>
+        <v>0.2007</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2552</v>
+        <v>0.2107</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2855</v>
+        <v>-0.2053</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3807</v>
+        <v>-0.0484</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7827</v>
+        <v>-0.8486</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1634</v>
+        <v>0.8002</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4214</v>
+        <v>1.1659</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7259</v>
+        <v>-1.84</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1472</v>
+        <v>3.0059</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3074</v>
+        <v>2.6043</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3994</v>
+        <v>-0.3476</v>
       </c>
       <c r="I7" t="n">
-        <v>0.092</v>
+        <v>2.9519</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7188</v>
+        <v>1.9531</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6</v>
+        <v>0.2565</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1188</v>
+        <v>1.6967</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4114</v>
+        <v>0.6512</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2007</v>
+        <v>-0.6041</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2107</v>
+        <v>1.2552</v>
       </c>
       <c r="P7" t="n">
+        <v>-2.2588</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-3.2855</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.0267</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.2321</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.4766</v>
+        <v>0.1222</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9804</v>
+        <v>-0.5077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5038</v>
+        <v>0.6298</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1786</v>
+        <v>0.6982</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="G8" t="n">
         <v>0.1395</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0307</v>
+        <v>0.0345</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0867</v>
+        <v>-1.3142</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1174</v>
+        <v>1.3487</v>
       </c>
       <c r="G9" t="n">
-        <v>1.375</v>
+        <v>1.7829</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5091</v>
+        <v>-0.7429</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8659</v>
+        <v>2.5258</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1268</v>
+        <v>1.1608</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.11</v>
+        <v>0.0297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2368</v>
+        <v>1.1311</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2482</v>
+        <v>0.6221</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6191</v>
+        <v>-0.7726</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>1.3947</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R9" t="n">
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>1.401</v>
+        <v>-0.4629</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0041</v>
+        <v>-0.3682</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4051</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3347</v>
+        <v>1.1786</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0225</v>
+        <v>1.1786</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6556</v>
+        <v>-0.2956</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5893</v>
+        <v>-1.8216</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9337</v>
+        <v>1.526</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7829</v>
+        <v>-0.5349</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7429</v>
+        <v>0.5966</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5258</v>
+        <v>-1.1315</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1608</v>
+        <v>-1.0857</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0297</v>
+        <v>0.2565</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1311</v>
+        <v>-1.3422</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6221</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7726</v>
+        <v>0.3401</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3947</v>
+        <v>0.2107</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4641</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R10" t="n">
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.153</v>
+        <v>0.4098</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6433</v>
+        <v>-0.3333</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5097</v>
+        <v>0.7431</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0.8295</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.746</v>
+        <v>-0.3087</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1238</v>
+        <v>-1.3075</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3778</v>
+        <v>0.9989</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5349</v>
+        <v>1.375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5966</v>
+        <v>0.5091</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1315</v>
+        <v>0.8659</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0857</v>
+        <v>0.1268</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2565</v>
+        <v>-0.11</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3422</v>
+        <v>0.2368</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5508999999999999</v>
+        <v>1.2482</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3401</v>
+        <v>0.6191</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2107</v>
+        <v>0.6291</v>
       </c>
       <c r="P11" t="n">
         <v>-0.4107</v>
@@ -1312,22 +1312,22 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0407</v>
+        <v>1.0617</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6355</v>
+        <v>-0.2249</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5949</v>
+        <v>1.2865</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2402</v>
+        <v>-2.3347</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8295</v>
+        <v>0.0225</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5893</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.1175</v>
+        <v>-7.8054</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3942</v>
+        <v>-7.2896</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.5158</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7918</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.3709</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>-0.4882</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0902</v>
+        <v>0.1173</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7679</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.297800000000001</v>
+        <v>7.285899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.5213</v>
+        <v>-10.5331</v>
       </c>
       <c r="F13" t="n">
-        <v>17.8189</v>
+        <v>17.8191</v>
       </c>
       <c r="G13" t="n">
         <v>10.9231</v>
@@ -1441,7 +1441,7 @@
         <v>14.5104</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8091</v>
+        <v>3.809100000000001</v>
       </c>
       <c r="K13" t="n">
         <v>-3.3713</v>
@@ -1450,13 +1450,13 @@
         <v>7.180599999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>7.113999999999999</v>
+        <v>7.114</v>
       </c>
       <c r="N13" t="n">
         <v>-0.2158999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>7.3297</v>
+        <v>7.329700000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-10.2671</v>
@@ -1468,19 +1468,19 @@
         <v>9.240600000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09759999999999991</v>
+        <v>1.0858</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.405900000000001</v>
+        <v>-4.4179</v>
       </c>
       <c r="U13" t="n">
-        <v>5.5036</v>
+        <v>5.5035</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5441</v>
+        <v>5.544100000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>9.582799999999999</v>
+        <v>9.582800000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-4.0389</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5124</v>
+        <v>3.1002</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3648</v>
+        <v>-1.2803</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1476</v>
+        <v>4.3805</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1653</v>
+        <v>-0.3457</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9044</v>
+        <v>0.4068</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7391</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8489</v>
+        <v>0.4399</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4278</v>
+        <v>0.151</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.579</v>
+        <v>0.2889</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3164</v>
+        <v>-0.7856</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4766</v>
+        <v>0.2559</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1602</v>
+        <v>-1.0415</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2053</v>
+        <v>2.6694</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2588</v>
+        <v>3.6962</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9488</v>
+        <v>-0.1619</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0191</v>
+        <v>-1.2828</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9297</v>
+        <v>1.1208</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5503</v>
+        <v>0.5893</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3573</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4143</v>
+        <v>0.8726</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2217</v>
+        <v>-0.3674</v>
       </c>
       <c r="F15" t="n">
-        <v>3.636</v>
+        <v>1.24</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3457</v>
+        <v>1.1653</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4068</v>
+        <v>1.9044</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7391</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4399</v>
+        <v>0.8489</v>
       </c>
       <c r="K15" t="n">
-        <v>0.151</v>
+        <v>1.4278</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2889</v>
+        <v>-0.579</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7856</v>
+        <v>0.3164</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2559</v>
+        <v>0.4766</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0415</v>
+        <v>-0.1602</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>3.6962</v>
+        <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8478</v>
+        <v>0.3089</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.2242</v>
+        <v>-0.7131</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3764</v>
+        <v>1.022</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9384</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5893</v>
+        <v>1.5503</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3491</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2889</v>
+        <v>0.2384</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3179</v>
+        <v>1.8995</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.029</v>
+        <v>-1.6611</v>
       </c>
       <c r="G16" t="n">
         <v>0.1341</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6558</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5461</v>
+        <v>0.1277</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1097</v>
+        <v>0.4776</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.234</v>
+        <v>-0.0311</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.7633</v>
+        <v>-3.554</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9973</v>
+        <v>3.523</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8214</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4743</v>
+        <v>0.2092</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.178</v>
+        <v>-0.9688</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6522</v>
+        <v>1.178</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9121</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8098</v>
+        <v>-2.6006</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8977</v>
+        <v>2.0668</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0709</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4491</v>
+        <v>-0.0708</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9145</v>
+        <v>-0.7053</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4654</v>
+        <v>0.6345</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4189</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3766</v>
+        <v>-1.1019</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6517</v>
+        <v>-0.0353</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2751</v>
+        <v>-1.0666</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7883</v>
+        <v>-0.8938</v>
       </c>
       <c r="H19" t="n">
-        <v>0.185</v>
+        <v>1.5926</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9733</v>
+        <v>-2.4863</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.71</v>
+        <v>0.6972</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0126</v>
+        <v>1.421</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6974</v>
+        <v>-0.7238</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0783</v>
+        <v>-1.591</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1977</v>
+        <v>0.1716</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2759</v>
+        <v>-1.7626</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4107</v>
+        <v>2.6694</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S19" t="n">
-        <v>2.001</v>
+        <v>-0.0398</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1117</v>
+        <v>-0.7325</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8893</v>
+        <v>0.6927</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>-2.8377</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>-2.8377</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>M. BECHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9963</v>
+        <v>-2.0792</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2445</v>
+        <v>-3.6354</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7518</v>
+        <v>1.5562</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8938</v>
+        <v>-4.9724</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5926</v>
+        <v>-0.6357</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4863</v>
+        <v>-4.3366</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6972</v>
+        <v>-3.9232</v>
       </c>
       <c r="K20" t="n">
-        <v>1.421</v>
+        <v>-0.3046</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7238</v>
+        <v>-3.6186</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.591</v>
+        <v>-1.0492</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1716</v>
+        <v>-0.3311</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7626</v>
+        <v>-0.7181</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6694</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9342</v>
+        <v>0.2217</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9417</v>
+        <v>-0.4535</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0075</v>
+        <v>0.6752</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8377</v>
+        <v>2.4661</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.8377</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.046</v>
+        <v>-2.2046</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4431</v>
+        <v>-5.6523</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3971</v>
+        <v>3.4477</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3302</v>
@@ -2092,13 +2092,13 @@
         <v>3.0801</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1692</v>
+        <v>0.0106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.9456</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9056</v>
+        <v>0.9562</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BECHT</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4164</v>
+        <v>-2.4662</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3676</v>
+        <v>-2.5931</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9512</v>
+        <v>0.1269</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9724</v>
+        <v>-1.7883</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6357</v>
+        <v>0.185</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3366</v>
+        <v>-1.9733</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.9232</v>
+        <v>-0.71</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3046</v>
+        <v>-0.0126</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.6186</v>
+        <v>-0.6974</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0492</v>
+        <v>-1.0783</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3311</v>
+        <v>0.1977</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7181</v>
+        <v>-1.2759</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1155</v>
+        <v>0.9113</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1857</v>
+        <v>0.1703</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0702</v>
+        <v>0.7411</v>
       </c>
       <c r="V22" t="n">
-        <v>2.4661</v>
+        <v>-1.1786</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2978</v>
+        <v>-4.2056</v>
       </c>
       <c r="E23" t="n">
-        <v>-17.819</v>
+        <v>-17.8189</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5212</v>
+        <v>13.6134</v>
       </c>
       <c r="G23" t="n">
         <v>-10.9233</v>
@@ -2224,7 +2224,7 @@
         <v>-7.114000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2159000000000002</v>
+        <v>0.2159000000000003</v>
       </c>
       <c r="L23" t="n">
         <v>-7.329899999999999</v>
@@ -2233,7 +2233,7 @@
         <v>-3.8093</v>
       </c>
       <c r="N23" t="n">
-        <v>3.371499999999999</v>
+        <v>3.3715</v>
       </c>
       <c r="O23" t="n">
         <v>-7.1806</v>
@@ -2248,13 +2248,13 @@
         <v>19.5075</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.09750000000000014</v>
+        <v>1.9945</v>
       </c>
       <c r="T23" t="n">
         <v>-5.5036</v>
       </c>
       <c r="U23" t="n">
-        <v>5.405999999999999</v>
+        <v>7.4981</v>
       </c>
       <c r="V23" t="n">
         <v>-5.544</v>
@@ -2263,7 +2263,7 @@
         <v>4.0389</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.5829</v>
+        <v>-9.582899999999999</v>
       </c>
     </row>
   </sheetData>
